--- a/research/traditional_assets/database/data/taiwan/taiwan_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05980000000000001</v>
+        <v>-0.1087</v>
       </c>
       <c r="E2">
-        <v>0.277</v>
+        <v>0.1595</v>
       </c>
       <c r="F2">
-        <v>0.0774</v>
+        <v>-0.07769999999999999</v>
       </c>
       <c r="G2">
-        <v>0.189071762101352</v>
+        <v>0.4256807579276187</v>
       </c>
       <c r="H2">
-        <v>0.189071762101352</v>
+        <v>0.4256807579276187</v>
       </c>
       <c r="I2">
-        <v>0.204159456598663</v>
+        <v>-0.3964323146797098</v>
       </c>
       <c r="J2">
-        <v>0.191951964094412</v>
+        <v>-0.3367863155885895</v>
       </c>
       <c r="K2">
-        <v>12539.3</v>
+        <v>6587.5</v>
       </c>
       <c r="L2">
-        <v>0.1094211264373233</v>
+        <v>0.1353809161717257</v>
       </c>
       <c r="M2">
-        <v>2878.41</v>
+        <v>3520.3884</v>
       </c>
       <c r="N2">
-        <v>0.03330313569499691</v>
+        <v>0.0609339943019154</v>
       </c>
       <c r="O2">
-        <v>0.2295510913687367</v>
+        <v>0.534404311195446</v>
       </c>
       <c r="P2">
-        <v>2875.8</v>
+        <v>3520.3884</v>
       </c>
       <c r="Q2">
-        <v>0.03327293805666049</v>
+        <v>0.0609339943019154</v>
       </c>
       <c r="R2">
-        <v>0.2293429457784725</v>
+        <v>0.534404311195446</v>
       </c>
       <c r="S2">
-        <v>2.6099999999999</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.0009067506018947614</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>43839.1</v>
+        <v>30731.2</v>
       </c>
       <c r="V2">
-        <v>0.5072173512621687</v>
+        <v>0.5319227746833339</v>
       </c>
       <c r="W2">
-        <v>0.1731519415907945</v>
+        <v>0.07455962294416445</v>
       </c>
       <c r="X2">
-        <v>0.08204116421122412</v>
+        <v>0.1355992432226285</v>
       </c>
       <c r="Y2">
-        <v>0.09111077737957035</v>
+        <v>-0.061039620278464</v>
       </c>
       <c r="Z2">
-        <v>1.600484628410817</v>
+        <v>0.5351082665259037</v>
       </c>
       <c r="AA2">
-        <v>0.2702793924465992</v>
+        <v>-0.2524268414112724</v>
       </c>
       <c r="AB2">
-        <v>0.0609206576707582</v>
+        <v>0.09446812048907141</v>
       </c>
       <c r="AC2">
-        <v>0.2081911354972449</v>
+        <v>-0.3477718541570409</v>
       </c>
       <c r="AD2">
-        <v>54224.7</v>
+        <v>58777.55</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>54224.7</v>
+        <v>58777.55</v>
       </c>
       <c r="AG2">
-        <v>10385.60000000001</v>
+        <v>28046.34999999999</v>
       </c>
       <c r="AH2">
-        <v>0.3855148010775279</v>
+        <v>0.5043060419291582</v>
       </c>
       <c r="AI2">
-        <v>0.3834115009237988</v>
+        <v>0.5861597506473406</v>
       </c>
       <c r="AJ2">
-        <v>0.1072713037694106</v>
+        <v>0.3268037867563736</v>
       </c>
       <c r="AK2">
-        <v>0.1064231389579436</v>
+        <v>0.4032866749251737</v>
       </c>
       <c r="AL2">
-        <v>1587.011</v>
+        <v>1910.884</v>
       </c>
       <c r="AM2">
-        <v>1587.011</v>
+        <v>1910.884</v>
       </c>
       <c r="AN2">
-        <v>2.275805192515928</v>
+        <v>-3.108180068321471</v>
       </c>
       <c r="AO2">
-        <v>14.74217885068219</v>
+        <v>-10.09480428953301</v>
       </c>
       <c r="AP2">
-        <v>0.4358825850100311</v>
+        <v>-1.483102069738665</v>
       </c>
       <c r="AQ2">
-        <v>14.74217885068219</v>
+        <v>-10.09480428953301</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Farglory Life Insurance Co., Ltd. (TPEX:5859)</t>
+          <t>China Development Financial Holding Corporation (TWSE:2883)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,118 +725,109 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.145</v>
+        <v>-0.00513</v>
       </c>
       <c r="E3">
-        <v>0.426</v>
+        <v>0.187</v>
       </c>
       <c r="G3">
-        <v>0.1507756710169909</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.1507756710169909</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.1953213494213248</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.1648583866675402</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>211.6</v>
+        <v>776.1</v>
       </c>
       <c r="L3">
-        <v>0.05210539276040384</v>
+        <v>0.604345117582931</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>530</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.07670265420127934</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.6829016879268135</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>530</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.07670265420127934</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.6829016879268135</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>312.7</v>
+        <v>2925.5</v>
       </c>
       <c r="V3">
-        <v>0.5209062135598868</v>
+        <v>0.4233841789921561</v>
       </c>
       <c r="W3">
-        <v>0.2245331069609508</v>
+        <v>0.09722274418429855</v>
       </c>
       <c r="X3">
-        <v>0.06161934656852328</v>
+        <v>0.1903761537683513</v>
       </c>
       <c r="Y3">
-        <v>0.1629137603924275</v>
+        <v>-0.0931534095840528</v>
       </c>
       <c r="Z3">
-        <v>6.024775610117945</v>
+        <v>0.08780794661233086</v>
       </c>
       <c r="AA3">
-        <v>0.9932347871179895</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0609206576707582</v>
+        <v>0.09658529696078925</v>
       </c>
       <c r="AC3">
-        <v>0.9323141294472314</v>
+        <v>-0.09658529696078925</v>
       </c>
       <c r="AD3">
-        <v>11</v>
+        <v>14837.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11</v>
+        <v>14837.6</v>
       </c>
       <c r="AG3">
-        <v>-301.7</v>
+        <v>11912.1</v>
       </c>
       <c r="AH3">
-        <v>0.01799443808277442</v>
+        <v>0.6822700644674765</v>
       </c>
       <c r="AI3">
-        <v>0.007686395080707149</v>
+        <v>0.7368583106131713</v>
       </c>
       <c r="AJ3">
-        <v>-1.010381781647689</v>
+        <v>0.6328850966161758</v>
       </c>
       <c r="AK3">
-        <v>-0.2697603719599428</v>
+        <v>0.6921293606340205</v>
       </c>
       <c r="AL3">
-        <v>0.231</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.231</v>
-      </c>
-      <c r="AN3">
-        <v>0.01362735381565907</v>
-      </c>
-      <c r="AO3">
-        <v>3433.766233766234</v>
-      </c>
-      <c r="AP3">
-        <v>-0.3737611496531218</v>
-      </c>
-      <c r="AQ3">
-        <v>3433.766233766234</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Shin Kong Financial Holding Co., Ltd. (TWSE:2888)</t>
+          <t>Fubon Financial Holding Co., Ltd. (TWSE:2881)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,49 +847,49 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0283</v>
+        <v>-0.0574</v>
       </c>
       <c r="E4">
-        <v>0.414</v>
+        <v>0.132</v>
       </c>
       <c r="F4">
-        <v>0.15</v>
+        <v>-0.07769999999999999</v>
       </c>
       <c r="G4">
-        <v>0.1978402646207332</v>
+        <v>0.4565700001748038</v>
       </c>
       <c r="H4">
-        <v>0.1978402646207332</v>
+        <v>0.4565700001748038</v>
       </c>
       <c r="I4">
-        <v>0.1608608927823319</v>
+        <v>-0.1455124955570705</v>
       </c>
       <c r="J4">
-        <v>0.1608608927823319</v>
+        <v>-0.1196490681975152</v>
       </c>
       <c r="K4">
-        <v>658.7</v>
+        <v>3063.6</v>
       </c>
       <c r="L4">
-        <v>0.04118754181595353</v>
+        <v>0.1785096229482406</v>
       </c>
       <c r="M4">
-        <v>244.3</v>
+        <v>1299.7</v>
       </c>
       <c r="N4">
-        <v>0.04276661298228416</v>
+        <v>0.05067471410914734</v>
       </c>
       <c r="O4">
-        <v>0.3708820403825717</v>
+        <v>0.4242394568481525</v>
       </c>
       <c r="P4">
-        <v>244.3</v>
+        <v>1299.7</v>
       </c>
       <c r="Q4">
-        <v>0.04276661298228416</v>
+        <v>0.05067471410914734</v>
       </c>
       <c r="R4">
-        <v>0.3708820403825717</v>
+        <v>0.4242394568481525</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -907,73 +898,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>3520.9</v>
+        <v>9018.200000000001</v>
       </c>
       <c r="V4">
-        <v>0.616360899096702</v>
+        <v>0.3516155318759041</v>
       </c>
       <c r="W4">
-        <v>0.0789438991358957</v>
+        <v>0.1026073850791258</v>
       </c>
       <c r="X4">
-        <v>0.0919401426299309</v>
+        <v>0.1231351435580359</v>
       </c>
       <c r="Y4">
-        <v>-0.01299624349403521</v>
+        <v>-0.02052775847891004</v>
       </c>
       <c r="Z4">
-        <v>2.844916837143112</v>
+        <v>0.415568346090237</v>
       </c>
       <c r="AA4">
-        <v>0.457635862314329</v>
+        <v>-0.04972236538207937</v>
       </c>
       <c r="AB4">
-        <v>0.06027026880601771</v>
+        <v>0.09512981909569598</v>
       </c>
       <c r="AC4">
-        <v>0.3973655935083112</v>
+        <v>-0.1448521844777754</v>
       </c>
       <c r="AD4">
-        <v>4827</v>
+        <v>16420.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>4827</v>
+        <v>16420.6</v>
       </c>
       <c r="AG4">
-        <v>1306.1</v>
+        <v>7402.399999999998</v>
       </c>
       <c r="AH4">
-        <v>0.4579957113308158</v>
+        <v>0.3903300569309578</v>
       </c>
       <c r="AI4">
-        <v>0.3498130272197583</v>
+        <v>0.4766543685431223</v>
       </c>
       <c r="AJ4">
-        <v>0.1860938947068462</v>
+        <v>0.2239737612064035</v>
       </c>
       <c r="AK4">
-        <v>0.1270784887963494</v>
+        <v>0.2910720956294359</v>
       </c>
       <c r="AL4">
-        <v>186.9</v>
+        <v>1142.3</v>
       </c>
       <c r="AM4">
-        <v>186.9</v>
+        <v>1142.3</v>
       </c>
       <c r="AN4">
-        <v>1.847726228755168</v>
+        <v>-6.939063556457064</v>
       </c>
       <c r="AO4">
-        <v>13.76457998929909</v>
+        <v>-2.186203274096122</v>
       </c>
       <c r="AP4">
-        <v>0.4999617210228142</v>
+        <v>-3.12812711291413</v>
       </c>
       <c r="AQ4">
-        <v>13.76457998929909</v>
+        <v>-2.186203274096122</v>
       </c>
     </row>
     <row r="5">
@@ -984,7 +975,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cathay Financial Holding Co., Ltd. (TWSE:2882)</t>
+          <t>Farglory Life Insurance Co., Ltd. (TPEX:5859)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -993,49 +984,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.105</v>
+        <v>-0.0228</v>
       </c>
       <c r="E5">
-        <v>0.277</v>
-      </c>
-      <c r="F5">
-        <v>0.0774</v>
+        <v>0.541</v>
       </c>
       <c r="G5">
-        <v>0.2006157875532941</v>
+        <v>0.2677002583979328</v>
       </c>
       <c r="H5">
-        <v>0.2006157875532941</v>
+        <v>0.2677002583979328</v>
       </c>
       <c r="I5">
-        <v>0.2344341202285211</v>
+        <v>-0.03840190816935003</v>
       </c>
       <c r="J5">
-        <v>0.2115404036667188</v>
+        <v>-0.03417577313328644</v>
       </c>
       <c r="K5">
-        <v>4771.6</v>
+        <v>372.8</v>
       </c>
       <c r="L5">
-        <v>0.1192488591435955</v>
+        <v>0.1482011528523156</v>
       </c>
       <c r="M5">
-        <v>1182.7</v>
+        <v>42.2484</v>
       </c>
       <c r="N5">
-        <v>0.03985603704215433</v>
+        <v>0.08035070368961582</v>
       </c>
       <c r="O5">
-        <v>0.2478623522508173</v>
+        <v>0.1133272532188841</v>
       </c>
       <c r="P5">
-        <v>1182.7</v>
+        <v>42.2484</v>
       </c>
       <c r="Q5">
-        <v>0.03985603704215433</v>
+        <v>0.08035070368961582</v>
       </c>
       <c r="R5">
-        <v>0.2478623522508173</v>
+        <v>0.1133272532188841</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1044,73 +1032,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>21171.4</v>
+        <v>525</v>
       </c>
       <c r="V5">
-        <v>0.7134591211924124</v>
+        <v>0.9984785089387601</v>
       </c>
       <c r="W5">
-        <v>0.1731519415907945</v>
+        <v>0.262516724174354</v>
       </c>
       <c r="X5">
-        <v>0.07926854548768622</v>
+        <v>0.09531284630515335</v>
       </c>
       <c r="Y5">
-        <v>0.09388339610310825</v>
+        <v>0.1672038778692006</v>
       </c>
       <c r="Z5">
-        <v>1.897143886665782</v>
+        <v>2.249195278969957</v>
       </c>
       <c r="AA5">
-        <v>0.4013225835991274</v>
+        <v>-0.07686798758653618</v>
       </c>
       <c r="AB5">
-        <v>0.06198824155847431</v>
+        <v>0.09446812048907141</v>
       </c>
       <c r="AC5">
-        <v>0.3393343420406531</v>
+        <v>-0.1713361080756076</v>
       </c>
       <c r="AD5">
-        <v>14822.9</v>
+        <v>8.75</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>14822.9</v>
+        <v>8.75</v>
       </c>
       <c r="AG5">
-        <v>-6348.500000000002</v>
+        <v>-516.25</v>
       </c>
       <c r="AH5">
-        <v>0.3331198367537733</v>
+        <v>0.01636890842764943</v>
       </c>
       <c r="AI5">
-        <v>0.321703348576166</v>
+        <v>0.007720474698901488</v>
       </c>
       <c r="AJ5">
-        <v>-0.2721664423085169</v>
+        <v>-54.05759162303691</v>
       </c>
       <c r="AK5">
-        <v>-0.2549096764090601</v>
+        <v>-0.8486068874825349</v>
       </c>
       <c r="AL5">
-        <v>479.6</v>
+        <v>0.204</v>
       </c>
       <c r="AM5">
-        <v>479.6</v>
+        <v>0.204</v>
       </c>
       <c r="AN5">
-        <v>1.549556236214052</v>
+        <v>-0.1051682692307692</v>
       </c>
       <c r="AO5">
-        <v>19.55921601334445</v>
+        <v>-473.5294117647059</v>
       </c>
       <c r="AP5">
-        <v>-0.6636594570296577</v>
+        <v>6.204927884615384</v>
       </c>
       <c r="AQ5">
-        <v>19.55921601334445</v>
+        <v>-473.5294117647059</v>
       </c>
     </row>
     <row r="6">
@@ -1121,7 +1109,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fubon Financial Holding Co., Ltd. (TWSE:2881)</t>
+          <t>Cathay Financial Holding Co., Ltd. (TWSE:2882)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1129,125 +1117,119 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.05980000000000001</v>
-      </c>
-      <c r="E6">
-        <v>0.272</v>
-      </c>
       <c r="F6">
-        <v>0.06809999999999999</v>
+        <v>-0.114</v>
       </c>
       <c r="G6">
-        <v>0.2298964990992438</v>
+        <v>0.4937087976441455</v>
       </c>
       <c r="H6">
-        <v>0.2298964990992438</v>
+        <v>0.4937087976441455</v>
       </c>
       <c r="I6">
-        <v>0.2601205980562026</v>
+        <v>-0.4220404020122924</v>
       </c>
       <c r="J6">
-        <v>0.2318467104761076</v>
+        <v>-0.3338294224238869</v>
       </c>
       <c r="K6">
-        <v>5470.1</v>
+        <v>2259</v>
       </c>
       <c r="L6">
-        <v>0.1569180369252659</v>
+        <v>0.1259913663286819</v>
       </c>
       <c r="M6">
-        <v>1105.41</v>
+        <v>1449.9</v>
       </c>
       <c r="N6">
-        <v>0.03003162338826674</v>
+        <v>0.07591139220624192</v>
       </c>
       <c r="O6">
-        <v>0.2020822288440796</v>
+        <v>0.6418326693227092</v>
       </c>
       <c r="P6">
-        <v>1102.8</v>
+        <v>1449.9</v>
       </c>
       <c r="Q6">
-        <v>0.02996071527540059</v>
+        <v>0.07591139220624192</v>
       </c>
       <c r="R6">
-        <v>0.201605089486481</v>
+        <v>0.6418326693227092</v>
       </c>
       <c r="S6">
-        <v>2.6099999999999</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.002361114880451507</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>9619.5</v>
+        <v>14119.9</v>
       </c>
       <c r="V6">
-        <v>0.2613412228796844</v>
+        <v>0.7392656506055004</v>
       </c>
       <c r="W6">
-        <v>0.2449795779441797</v>
+        <v>0.07455962294416445</v>
       </c>
       <c r="X6">
-        <v>0.08204116421122412</v>
+        <v>0.1470457211384008</v>
       </c>
       <c r="Y6">
-        <v>0.1629384137329556</v>
+        <v>-0.07248609819423636</v>
       </c>
       <c r="Z6">
-        <v>1.165767639711464</v>
+        <v>0.7561551632520518</v>
       </c>
       <c r="AA6">
-        <v>0.2702793924465992</v>
+        <v>-0.2524268414112724</v>
       </c>
       <c r="AB6">
-        <v>0.0620882569493542</v>
+        <v>0.09534501274576852</v>
       </c>
       <c r="AC6">
-        <v>0.2081911354972449</v>
+        <v>-0.3477718541570409</v>
       </c>
       <c r="AD6">
-        <v>21168.9</v>
+        <v>22464.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>21168.9</v>
+        <v>22464.3</v>
       </c>
       <c r="AG6">
-        <v>11549.4</v>
+        <v>8344.4</v>
       </c>
       <c r="AH6">
-        <v>0.3651251959825518</v>
+        <v>0.5404723295528363</v>
       </c>
       <c r="AI6">
-        <v>0.4022249878870215</v>
+        <v>0.6995935908814873</v>
       </c>
       <c r="AJ6">
-        <v>0.2388331927142787</v>
+        <v>0.304048563818352</v>
       </c>
       <c r="AK6">
-        <v>0.2685282492443618</v>
+        <v>0.4638199948862184</v>
       </c>
       <c r="AL6">
-        <v>905.1</v>
+        <v>550.3</v>
       </c>
       <c r="AM6">
-        <v>905.1</v>
+        <v>550.3</v>
       </c>
       <c r="AN6">
-        <v>2.298394189114362</v>
+        <v>-3.03161943319838</v>
       </c>
       <c r="AO6">
-        <v>10.01845099988951</v>
+        <v>-13.75086316554607</v>
       </c>
       <c r="AP6">
-        <v>1.253965668870721</v>
+        <v>-1.126099865047233</v>
       </c>
       <c r="AQ6">
-        <v>10.01845099988951</v>
+        <v>-13.75086316554607</v>
       </c>
     </row>
     <row r="7">
@@ -1258,7 +1240,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>China Development Financial Holding Corporation (TWSE:2883)</t>
+          <t>Shin Kong Financial Holding Co., Ltd. (TWSE:2888)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1267,46 +1249,49 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.488</v>
+        <v>-0.16</v>
       </c>
       <c r="E7">
-        <v>0.381</v>
+        <v>-0.0359</v>
+      </c>
+      <c r="F7">
+        <v>0.15</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.4037638538351805</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.4037638538351805</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>-0.830718021873514</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>-0.5650011923694104</v>
       </c>
       <c r="K7">
-        <v>1241.3</v>
+        <v>357.4</v>
       </c>
       <c r="L7">
-        <v>0.1715474232645559</v>
+        <v>0.06536449760415523</v>
       </c>
       <c r="M7">
-        <v>296.2</v>
+        <v>195</v>
       </c>
       <c r="N7">
-        <v>0.02460173757039153</v>
+        <v>0.04410467509556013</v>
       </c>
       <c r="O7">
-        <v>0.2386208007733827</v>
+        <v>0.5456071628427532</v>
       </c>
       <c r="P7">
-        <v>296.2</v>
+        <v>195</v>
       </c>
       <c r="Q7">
-        <v>0.02460173757039153</v>
+        <v>0.04410467509556013</v>
       </c>
       <c r="R7">
-        <v>0.2386208007733827</v>
+        <v>0.5456071628427532</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1315,61 +1300,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>5470.9</v>
+        <v>2868.2</v>
       </c>
       <c r="V7">
-        <v>0.4544012359009286</v>
+        <v>0.6487232262004388</v>
       </c>
       <c r="W7">
-        <v>0.1939016198822188</v>
+        <v>0.04038007434272221</v>
       </c>
       <c r="X7">
-        <v>0.09818742287436943</v>
+        <v>0.1355992432226285</v>
       </c>
       <c r="Y7">
-        <v>0.09571419700784936</v>
+        <v>-0.09521916887990625</v>
       </c>
       <c r="Z7">
-        <v>0.4385872398201016</v>
+        <v>0.5371225367885419</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>-0.3034748737340087</v>
       </c>
       <c r="AB7">
-        <v>0.06329169987003175</v>
+        <v>0.09157783398265038</v>
       </c>
       <c r="AC7">
-        <v>-0.06329169987003175</v>
+        <v>-0.3950527077166591</v>
       </c>
       <c r="AD7">
-        <v>12224.4</v>
+        <v>4065.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>12224.4</v>
+        <v>4065.8</v>
       </c>
       <c r="AG7">
-        <v>6753.5</v>
+        <v>1197.6</v>
       </c>
       <c r="AH7">
-        <v>0.5038039580946415</v>
+        <v>0.4790564503776319</v>
       </c>
       <c r="AI7">
-        <v>0.5273706961634864</v>
+        <v>0.4226051887576917</v>
       </c>
       <c r="AJ7">
-        <v>0.35935679204823</v>
+        <v>0.2131378027727847</v>
       </c>
       <c r="AK7">
-        <v>0.3813597605737196</v>
+        <v>0.1773539081242781</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>204.5</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>204.5</v>
+      </c>
+      <c r="AN7">
+        <v>-0.9022079218906025</v>
+      </c>
+      <c r="AO7">
+        <v>-22.21124694376528</v>
+      </c>
+      <c r="AP7">
+        <v>-0.2657494729834684</v>
+      </c>
+      <c r="AQ7">
+        <v>-22.21124694376528</v>
       </c>
     </row>
     <row r="8">
@@ -1389,46 +1386,43 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.0133</v>
-      </c>
-      <c r="E8">
-        <v>0.053</v>
+        <v>-0.165</v>
       </c>
       <c r="G8">
-        <v>0.1416080536513554</v>
+        <v>0.2314895223711535</v>
       </c>
       <c r="H8">
-        <v>0.1416080536513554</v>
+        <v>0.2314895223711535</v>
       </c>
       <c r="I8">
-        <v>0.1178158783030231</v>
+        <v>-0.8531244100434208</v>
       </c>
       <c r="J8">
-        <v>0.1178158783030231</v>
+        <v>-0.8531244100434208</v>
       </c>
       <c r="K8">
-        <v>76.5</v>
+        <v>-36</v>
       </c>
       <c r="L8">
-        <v>0.01137563383842139</v>
+        <v>-0.01359259958467057</v>
       </c>
       <c r="M8">
-        <v>49.8</v>
+        <v>3.54</v>
       </c>
       <c r="N8">
-        <v>0.07050828259946199</v>
+        <v>0.008209647495361782</v>
       </c>
       <c r="O8">
-        <v>0.6509803921568627</v>
+        <v>-0.09833333333333333</v>
       </c>
       <c r="P8">
-        <v>49.8</v>
+        <v>3.54</v>
       </c>
       <c r="Q8">
-        <v>0.07050828259946199</v>
+        <v>0.008209647495361782</v>
       </c>
       <c r="R8">
-        <v>0.6509803921568627</v>
+        <v>-0.09833333333333333</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1437,73 +1431,64 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>1903.3</v>
+        <v>660.3</v>
       </c>
       <c r="V8">
-        <v>2.694747274529237</v>
+        <v>1.531307977736549</v>
       </c>
       <c r="W8">
-        <v>0.1213322759714512</v>
+        <v>-0.05378753922008069</v>
       </c>
       <c r="X8">
-        <v>0.1053833282512603</v>
+        <v>0.1677444127800011</v>
       </c>
       <c r="Y8">
-        <v>0.01594894772019093</v>
-      </c>
-      <c r="Z8">
-        <v>-5.472737630208334</v>
-      </c>
-      <c r="AA8">
-        <v>-0.6447753906250001</v>
+        <v>-0.2215319520000818</v>
       </c>
       <c r="AB8">
-        <v>0.06013748995009732</v>
-      </c>
-      <c r="AC8">
-        <v>-0.7049128805750975</v>
+        <v>0.09068975865201341</v>
       </c>
       <c r="AD8">
-        <v>855.7</v>
+        <v>707.2</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>855.7</v>
+        <v>707.2</v>
       </c>
       <c r="AG8">
-        <v>-1047.6</v>
+        <v>46.90000000000009</v>
       </c>
       <c r="AH8">
-        <v>0.5478233034571063</v>
+        <v>0.6212227687983134</v>
       </c>
       <c r="AI8">
-        <v>0.3417741742221513</v>
+        <v>0.4154135338345865</v>
       </c>
       <c r="AJ8">
-        <v>3.069440375036625</v>
+        <v>0.09809663250366049</v>
       </c>
       <c r="AK8">
-        <v>-1.744836775483011</v>
+        <v>0.04500527780443344</v>
       </c>
       <c r="AL8">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="AM8">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="AN8">
-        <v>1.030467244701349</v>
+        <v>-0.3176142998293363</v>
       </c>
       <c r="AO8">
-        <v>199.0703517587939</v>
+        <v>-594.6052631578948</v>
       </c>
       <c r="AP8">
-        <v>-1.261560693641618</v>
+        <v>-0.02106350489535619</v>
       </c>
       <c r="AQ8">
-        <v>199.0703517587939</v>
+        <v>-594.6052631578948</v>
       </c>
     </row>
     <row r="9">
@@ -1514,7 +1499,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mercuries Life Insurance Co., Ltd. (TWSE:2867)</t>
+          <t>Mercuries Life Insurance Company Ltd. (TWSE:2867)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1523,28 +1508,25 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.021</v>
-      </c>
-      <c r="E9">
-        <v>0.00179</v>
+        <v>-0.22</v>
       </c>
       <c r="G9">
-        <v>0.1571083239910314</v>
+        <v>0.3217249106656169</v>
       </c>
       <c r="H9">
-        <v>0.1571083239910314</v>
+        <v>0.3217249106656169</v>
       </c>
       <c r="I9">
-        <v>0.1383127802690583</v>
+        <v>-1.409545151717037</v>
       </c>
       <c r="J9">
-        <v>0.1383127802690583</v>
+        <v>-1.409545151717037</v>
       </c>
       <c r="K9">
-        <v>109.5</v>
+        <v>-205.4</v>
       </c>
       <c r="L9">
-        <v>0.01918091367713004</v>
+        <v>-0.1244019138755981</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1553,7 +1535,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1562,79 +1544,70 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>1840.4</v>
+        <v>614.1</v>
       </c>
       <c r="V9">
-        <v>2.069492859552457</v>
+        <v>0.8322265889686949</v>
       </c>
       <c r="W9">
-        <v>0.08292313517606967</v>
+        <v>-0.137593783494105</v>
       </c>
       <c r="X9">
-        <v>0.07393069597233619</v>
+        <v>0.1110951515452498</v>
       </c>
       <c r="Y9">
-        <v>0.008992439203733479</v>
-      </c>
-      <c r="Z9">
-        <v>-5.959081419624217</v>
-      </c>
-      <c r="AA9">
-        <v>-0.8242171189979124</v>
+        <v>-0.2486889350393548</v>
       </c>
       <c r="AB9">
-        <v>0.0605608079518549</v>
-      </c>
-      <c r="AC9">
-        <v>-0.8847779269497673</v>
+        <v>0.09288204924525259</v>
       </c>
       <c r="AD9">
-        <v>314.8</v>
+        <v>273.3</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>314.8</v>
+        <v>273.3</v>
       </c>
       <c r="AG9">
-        <v>-1525.6</v>
+        <v>-340.8</v>
       </c>
       <c r="AH9">
-        <v>0.2614400797275974</v>
+        <v>0.2702729430379747</v>
       </c>
       <c r="AI9">
-        <v>0.1741535737995132</v>
+        <v>0.243452699091395</v>
       </c>
       <c r="AJ9">
-        <v>2.397611189690397</v>
+        <v>-0.8582221102996728</v>
       </c>
       <c r="AK9">
-        <v>46.51219512195097</v>
+        <v>-0.6702064896755163</v>
       </c>
       <c r="AL9">
-        <v>11.2</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AM9">
-        <v>11.2</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AN9">
-        <v>0.3933033483258371</v>
+        <v>-0.1179084516156866</v>
       </c>
       <c r="AO9">
-        <v>70.5</v>
+        <v>-237.9652351738242</v>
       </c>
       <c r="AP9">
-        <v>-1.906046976511744</v>
+        <v>0.1470296388972777</v>
       </c>
       <c r="AQ9">
-        <v>70.5</v>
+        <v>-237.9652351738242</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/taiwan/taiwan_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_insurance_life.xlsx
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.1087</v>
+        <v>-0.073</v>
       </c>
       <c r="E2">
-        <v>0.1595</v>
+        <v>-0.0427</v>
       </c>
       <c r="F2">
-        <v>-0.07769999999999999</v>
+        <v>0.204</v>
       </c>
       <c r="G2">
-        <v>0.4256807579276187</v>
+        <v>-0.2808894009293091</v>
       </c>
       <c r="H2">
-        <v>0.4256807579276187</v>
+        <v>-0.2808894009293091</v>
       </c>
       <c r="I2">
-        <v>-0.3964323146797098</v>
+        <v>0.02139170594123672</v>
       </c>
       <c r="J2">
-        <v>-0.3367863155885895</v>
+        <v>0.02024134000881314</v>
       </c>
       <c r="K2">
-        <v>6587.5</v>
+        <v>1975.3</v>
       </c>
       <c r="L2">
-        <v>0.1353809161717257</v>
+        <v>0.03279143003703624</v>
       </c>
       <c r="M2">
-        <v>3520.3884</v>
+        <v>1056.9</v>
       </c>
       <c r="N2">
-        <v>0.0609339943019154</v>
+        <v>0.01599187771789292</v>
       </c>
       <c r="O2">
-        <v>0.534404311195446</v>
+        <v>0.5350579658786007</v>
       </c>
       <c r="P2">
-        <v>3520.3884</v>
+        <v>1056.9</v>
       </c>
       <c r="Q2">
-        <v>0.0609339943019154</v>
+        <v>0.01599187771789292</v>
       </c>
       <c r="R2">
-        <v>0.534404311195446</v>
+        <v>0.5350579658786007</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>30731.2</v>
+        <v>34403.2</v>
       </c>
       <c r="V2">
-        <v>0.5319227746833339</v>
+        <v>0.5205523393927656</v>
       </c>
       <c r="W2">
-        <v>0.07455962294416445</v>
+        <v>-0.03281166637026498</v>
       </c>
       <c r="X2">
-        <v>0.1355992432226285</v>
+        <v>0.1167021088638113</v>
       </c>
       <c r="Y2">
-        <v>-0.061039620278464</v>
+        <v>-0.1495137752340763</v>
       </c>
       <c r="Z2">
-        <v>0.5351082665259037</v>
+        <v>0.9064599887592178</v>
       </c>
       <c r="AA2">
-        <v>-0.2524268414112724</v>
+        <v>-0.1597911853829768</v>
       </c>
       <c r="AB2">
-        <v>0.09446812048907141</v>
+        <v>0.08125388517380022</v>
       </c>
       <c r="AC2">
-        <v>-0.3477718541570409</v>
+        <v>-0.2380528735434169</v>
       </c>
       <c r="AD2">
-        <v>58777.55</v>
+        <v>62248.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>58777.55</v>
+        <v>62248.7</v>
       </c>
       <c r="AG2">
-        <v>28046.34999999999</v>
+        <v>27845.5</v>
       </c>
       <c r="AH2">
-        <v>0.5043060419291582</v>
+        <v>0.4850352778005041</v>
       </c>
       <c r="AI2">
-        <v>0.5861597506473406</v>
+        <v>0.4975644809075127</v>
       </c>
       <c r="AJ2">
-        <v>0.3268037867563736</v>
+        <v>0.2964327574404936</v>
       </c>
       <c r="AK2">
-        <v>0.4032866749251737</v>
+        <v>0.3069944302100467</v>
       </c>
       <c r="AL2">
-        <v>1910.884</v>
+        <v>5131.546</v>
       </c>
       <c r="AM2">
-        <v>1910.884</v>
+        <v>5131.546</v>
       </c>
       <c r="AN2">
-        <v>-3.108180068321471</v>
+        <v>36.4923789424317</v>
       </c>
       <c r="AO2">
-        <v>-10.09480428953301</v>
+        <v>0.2511134071486448</v>
       </c>
       <c r="AP2">
-        <v>-1.483102069738665</v>
+        <v>16.32401219369211</v>
       </c>
       <c r="AQ2">
-        <v>-10.09480428953301</v>
+        <v>0.2511134071486448</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>China Development Financial Holding Corporation (TWSE:2883)</t>
+          <t>Fubon Financial Holding Co., Ltd. (TWSE:2881)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,46 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00513</v>
+        <v>0.0617</v>
       </c>
       <c r="E3">
-        <v>0.187</v>
+        <v>-0.124</v>
+      </c>
+      <c r="F3">
+        <v>0.204</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>-0.09763021830716201</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>-0.09763021830716201</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.1512351589429337</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.1305132350611976</v>
       </c>
       <c r="K3">
-        <v>776.1</v>
+        <v>964.1</v>
       </c>
       <c r="L3">
-        <v>0.604345117582931</v>
+        <v>0.04615568747606281</v>
       </c>
       <c r="M3">
-        <v>530</v>
+        <v>577.8</v>
       </c>
       <c r="N3">
-        <v>0.07670265420127934</v>
+        <v>0.01869249582670135</v>
       </c>
       <c r="O3">
-        <v>0.6829016879268135</v>
+        <v>0.5993154237112333</v>
       </c>
       <c r="P3">
-        <v>530</v>
+        <v>577.8</v>
       </c>
       <c r="Q3">
-        <v>0.07670265420127934</v>
+        <v>0.01869249582670135</v>
       </c>
       <c r="R3">
-        <v>0.6829016879268135</v>
+        <v>0.5993154237112333</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,61 +776,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2925.5</v>
+        <v>9047.700000000001</v>
       </c>
       <c r="V3">
-        <v>0.4233841789921561</v>
+        <v>0.2927035210994216</v>
       </c>
       <c r="W3">
-        <v>0.09722274418429855</v>
+        <v>0.05717284690059242</v>
       </c>
       <c r="X3">
-        <v>0.1903761537683513</v>
+        <v>0.1018252904872283</v>
       </c>
       <c r="Y3">
-        <v>-0.0931534095840528</v>
+        <v>-0.04465244358663588</v>
       </c>
       <c r="Z3">
-        <v>0.08780794661233086</v>
+        <v>0.8605020968765191</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.1123069124402985</v>
       </c>
       <c r="AB3">
-        <v>0.09658529696078925</v>
+        <v>0.08130099504511885</v>
       </c>
       <c r="AC3">
-        <v>-0.09658529696078925</v>
+        <v>0.03100591739517969</v>
       </c>
       <c r="AD3">
-        <v>14837.6</v>
+        <v>18482.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>14837.6</v>
+        <v>18482.5</v>
       </c>
       <c r="AG3">
-        <v>11912.1</v>
+        <v>9434.799999999999</v>
       </c>
       <c r="AH3">
-        <v>0.6822700644674765</v>
+        <v>0.3741904266368111</v>
       </c>
       <c r="AI3">
-        <v>0.7368583106131713</v>
+        <v>0.4421597827777179</v>
       </c>
       <c r="AJ3">
-        <v>0.6328850966161758</v>
+        <v>0.2338495399746193</v>
       </c>
       <c r="AK3">
-        <v>0.6921293606340205</v>
+        <v>0.2880608680784543</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>2908.1</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>2908.1</v>
+      </c>
+      <c r="AN3">
+        <v>5.594654316503209</v>
+      </c>
+      <c r="AO3">
+        <v>1.086276262852034</v>
+      </c>
+      <c r="AP3">
+        <v>2.855914759656133</v>
+      </c>
+      <c r="AQ3">
+        <v>1.086276262852034</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fubon Financial Holding Co., Ltd. (TWSE:2881)</t>
+          <t>Cathay Financial Holding Co., Ltd. (TWSE:2882)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -846,50 +861,44 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>-0.0574</v>
-      </c>
-      <c r="E4">
-        <v>0.132</v>
-      </c>
       <c r="F4">
-        <v>-0.07769999999999999</v>
+        <v>0.212</v>
       </c>
       <c r="G4">
-        <v>0.4565700001748038</v>
+        <v>-0.2608286457493671</v>
       </c>
       <c r="H4">
-        <v>0.4565700001748038</v>
+        <v>-0.2608286457493671</v>
       </c>
       <c r="I4">
-        <v>-0.1455124955570705</v>
+        <v>0.0496368302491863</v>
       </c>
       <c r="J4">
-        <v>-0.1196490681975152</v>
+        <v>0.04281818148526557</v>
       </c>
       <c r="K4">
-        <v>3063.6</v>
+        <v>1327.5</v>
       </c>
       <c r="L4">
-        <v>0.1785096229482406</v>
+        <v>0.05784137303001651</v>
       </c>
       <c r="M4">
-        <v>1299.7</v>
+        <v>410.3</v>
       </c>
       <c r="N4">
-        <v>0.05067471410914734</v>
+        <v>0.01873122540470952</v>
       </c>
       <c r="O4">
-        <v>0.4242394568481525</v>
+        <v>0.3090772128060263</v>
       </c>
       <c r="P4">
-        <v>1299.7</v>
+        <v>410.3</v>
       </c>
       <c r="Q4">
-        <v>0.05067471410914734</v>
+        <v>0.01873122540470952</v>
       </c>
       <c r="R4">
-        <v>0.4242394568481525</v>
+        <v>0.3090772128060263</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,73 +907,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>9018.200000000001</v>
+        <v>19735.6</v>
       </c>
       <c r="V4">
-        <v>0.3516155318759041</v>
+        <v>0.9009797028934562</v>
       </c>
       <c r="W4">
-        <v>0.1026073850791258</v>
+        <v>0.1509586299438241</v>
       </c>
       <c r="X4">
-        <v>0.1231351435580359</v>
+        <v>0.1167021088638113</v>
       </c>
       <c r="Y4">
-        <v>-0.02052775847891004</v>
+        <v>0.03425652108001272</v>
       </c>
       <c r="Z4">
-        <v>0.415568346090237</v>
+        <v>1.359405078511393</v>
       </c>
       <c r="AA4">
-        <v>-0.04972236538207937</v>
+        <v>0.05820725336369253</v>
       </c>
       <c r="AB4">
-        <v>0.09512981909569598</v>
+        <v>0.08125388517380022</v>
       </c>
       <c r="AC4">
-        <v>-0.1448521844777754</v>
+        <v>-0.02304663181010769</v>
       </c>
       <c r="AD4">
-        <v>16420.6</v>
+        <v>22652.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>16420.6</v>
+        <v>22652.1</v>
       </c>
       <c r="AG4">
-        <v>7402.399999999998</v>
+        <v>2916.5</v>
       </c>
       <c r="AH4">
-        <v>0.3903300569309578</v>
+        <v>0.5083881885328132</v>
       </c>
       <c r="AI4">
-        <v>0.4766543685431223</v>
+        <v>0.5153744821137268</v>
       </c>
       <c r="AJ4">
-        <v>0.2239737612064035</v>
+        <v>0.1175008359822893</v>
       </c>
       <c r="AK4">
-        <v>0.2910720956294359</v>
+        <v>0.1204314306832775</v>
       </c>
       <c r="AL4">
-        <v>1142.3</v>
+        <v>1695.4</v>
       </c>
       <c r="AM4">
-        <v>1142.3</v>
+        <v>1695.4</v>
       </c>
       <c r="AN4">
-        <v>-6.939063556457064</v>
+        <v>17.16848567530695</v>
       </c>
       <c r="AO4">
-        <v>-2.186203274096122</v>
+        <v>0.6719358263536629</v>
       </c>
       <c r="AP4">
-        <v>-3.12812711291413</v>
+        <v>2.210474458087009</v>
       </c>
       <c r="AQ4">
-        <v>-2.186203274096122</v>
+        <v>0.6719358263536629</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +984,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Farglory Life Insurance Co., Ltd. (TPEX:5859)</t>
+          <t>China Development Financial Holding Corporation (TWSE:2883)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -983,122 +992,89 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>-0.0228</v>
-      </c>
       <c r="E5">
-        <v>0.541</v>
-      </c>
-      <c r="G5">
-        <v>0.2677002583979328</v>
-      </c>
-      <c r="H5">
-        <v>0.2677002583979328</v>
-      </c>
-      <c r="I5">
-        <v>-0.03840190816935003</v>
-      </c>
-      <c r="J5">
-        <v>-0.03417577313328644</v>
+        <v>0.0386</v>
       </c>
       <c r="K5">
-        <v>372.8</v>
-      </c>
-      <c r="L5">
-        <v>0.1482011528523156</v>
+        <v>421.3</v>
       </c>
       <c r="M5">
-        <v>42.2484</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.08035070368961582</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.1133272532188841</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>42.2484</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.08035070368961582</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.1133272532188841</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>525</v>
+        <v>2040.2</v>
       </c>
       <c r="V5">
-        <v>0.9984785089387601</v>
+        <v>0.2957797526711803</v>
       </c>
       <c r="W5">
-        <v>0.262516724174354</v>
+        <v>0.08794672678690715</v>
       </c>
       <c r="X5">
-        <v>0.09531284630515335</v>
+        <v>0.1548897717622041</v>
       </c>
       <c r="Y5">
-        <v>0.1672038778692006</v>
+        <v>-0.06694304497529699</v>
       </c>
       <c r="Z5">
-        <v>2.249195278969957</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>-0.07686798758653618</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.09446812048907141</v>
+        <v>0.08192197659248544</v>
       </c>
       <c r="AC5">
-        <v>-0.1713361080756076</v>
+        <v>-0.08192197659248544</v>
       </c>
       <c r="AD5">
-        <v>8.75</v>
+        <v>14856.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>8.75</v>
+        <v>14856.3</v>
       </c>
       <c r="AG5">
-        <v>-516.25</v>
+        <v>12816.1</v>
       </c>
       <c r="AH5">
-        <v>0.01636890842764943</v>
+        <v>0.6829226808862737</v>
       </c>
       <c r="AI5">
-        <v>0.007720474698901488</v>
+        <v>0.670099186749841</v>
       </c>
       <c r="AJ5">
-        <v>-54.05759162303691</v>
+        <v>0.6501080461402672</v>
       </c>
       <c r="AK5">
-        <v>-0.8486068874825349</v>
+        <v>0.6366635039070844</v>
       </c>
       <c r="AL5">
-        <v>0.204</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.204</v>
-      </c>
-      <c r="AN5">
-        <v>-0.1051682692307692</v>
-      </c>
-      <c r="AO5">
-        <v>-473.5294117647059</v>
-      </c>
-      <c r="AP5">
-        <v>6.204927884615384</v>
-      </c>
-      <c r="AQ5">
-        <v>-473.5294117647059</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1109,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cathay Financial Holding Co., Ltd. (TWSE:2882)</t>
+          <t>Shin Kong Financial Holding Co., Ltd. (TWSE:2888)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1117,119 +1093,119 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>-0.09130000000000001</v>
+      </c>
       <c r="F6">
-        <v>-0.114</v>
+        <v>0.15</v>
       </c>
       <c r="G6">
-        <v>0.4937087976441455</v>
+        <v>-0.5087360177493694</v>
       </c>
       <c r="H6">
-        <v>0.4937087976441455</v>
+        <v>-0.5087360177493694</v>
       </c>
       <c r="I6">
-        <v>-0.4220404020122924</v>
+        <v>-0.1406743175605182</v>
       </c>
       <c r="J6">
-        <v>-0.3338294224238869</v>
+        <v>-0.1406743175605182</v>
       </c>
       <c r="K6">
-        <v>2259</v>
+        <v>-279.3</v>
       </c>
       <c r="L6">
-        <v>0.1259913663286819</v>
+        <v>-0.03688540827511522</v>
       </c>
       <c r="M6">
-        <v>1449.9</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.07591139220624192</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.6418326693227092</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1449.9</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.07591139220624192</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.6418326693227092</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>14119.9</v>
+        <v>2263.5</v>
       </c>
       <c r="V6">
-        <v>0.7392656506055004</v>
+        <v>0.496436012720693</v>
       </c>
       <c r="W6">
-        <v>0.07455962294416445</v>
+        <v>-0.05125993356213409</v>
       </c>
       <c r="X6">
-        <v>0.1470457211384008</v>
+        <v>0.1187577066987725</v>
       </c>
       <c r="Y6">
-        <v>-0.07248609819423636</v>
+        <v>-0.1700176402609066</v>
       </c>
       <c r="Z6">
-        <v>0.7561551632520518</v>
+        <v>1.135894512615883</v>
       </c>
       <c r="AA6">
-        <v>-0.2524268414112724</v>
+        <v>-0.1597911853829768</v>
       </c>
       <c r="AB6">
-        <v>0.09534501274576852</v>
+        <v>0.07826168816044012</v>
       </c>
       <c r="AC6">
-        <v>-0.3477718541570409</v>
+        <v>-0.2380528735434169</v>
       </c>
       <c r="AD6">
-        <v>22464.3</v>
+        <v>4989.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>22464.3</v>
+        <v>4989.9</v>
       </c>
       <c r="AG6">
-        <v>8344.4</v>
+        <v>2726.4</v>
       </c>
       <c r="AH6">
-        <v>0.5404723295528363</v>
+        <v>0.5225354472532305</v>
       </c>
       <c r="AI6">
-        <v>0.6995935908814873</v>
+        <v>0.410343494815095</v>
       </c>
       <c r="AJ6">
-        <v>0.304048563818352</v>
+        <v>0.3742022262177631</v>
       </c>
       <c r="AK6">
-        <v>0.4638199948862184</v>
+        <v>0.2754829843989977</v>
       </c>
       <c r="AL6">
-        <v>550.3</v>
+        <v>509.7</v>
       </c>
       <c r="AM6">
-        <v>550.3</v>
+        <v>509.7</v>
       </c>
       <c r="AN6">
-        <v>-3.03161943319838</v>
+        <v>-4.849271137026239</v>
       </c>
       <c r="AO6">
-        <v>-13.75086316554607</v>
+        <v>-2.089856778497155</v>
       </c>
       <c r="AP6">
-        <v>-1.126099865047233</v>
+        <v>-2.649562682215743</v>
       </c>
       <c r="AQ6">
-        <v>-13.75086316554607</v>
+        <v>-2.089856778497155</v>
       </c>
     </row>
     <row r="7">
@@ -1240,7 +1216,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shin Kong Financial Holding Co., Ltd. (TWSE:2888)</t>
+          <t>Farglory Life Insurance Co., Ltd. (TPEX:5859)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1249,49 +1225,43 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.16</v>
-      </c>
-      <c r="E7">
-        <v>-0.0359</v>
-      </c>
-      <c r="F7">
-        <v>0.15</v>
+        <v>-0.0358</v>
       </c>
       <c r="G7">
-        <v>0.4037638538351805</v>
+        <v>-0.3656773211567733</v>
       </c>
       <c r="H7">
-        <v>0.4037638538351805</v>
+        <v>-0.3656773211567733</v>
       </c>
       <c r="I7">
-        <v>-0.830718021873514</v>
+        <v>-0.2511415525114155</v>
       </c>
       <c r="J7">
-        <v>-0.5650011923694104</v>
+        <v>-0.2511415525114155</v>
       </c>
       <c r="K7">
-        <v>357.4</v>
+        <v>-36.9</v>
       </c>
       <c r="L7">
-        <v>0.06536449760415523</v>
+        <v>-0.0200587084148728</v>
       </c>
       <c r="M7">
-        <v>195</v>
+        <v>39.9</v>
       </c>
       <c r="N7">
-        <v>0.04410467509556013</v>
+        <v>0.08083468395461912</v>
       </c>
       <c r="O7">
-        <v>0.5456071628427532</v>
+        <v>-1.08130081300813</v>
       </c>
       <c r="P7">
-        <v>195</v>
+        <v>39.9</v>
       </c>
       <c r="Q7">
-        <v>0.04410467509556013</v>
+        <v>0.08083468395461912</v>
       </c>
       <c r="R7">
-        <v>0.5456071628427532</v>
+        <v>-1.08130081300813</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1300,73 +1270,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>2868.2</v>
+        <v>267.9</v>
       </c>
       <c r="V7">
-        <v>0.6487232262004388</v>
+        <v>0.5427471636952997</v>
       </c>
       <c r="W7">
-        <v>0.04038007434272221</v>
+        <v>-0.03281166637026498</v>
       </c>
       <c r="X7">
-        <v>0.1355992432226285</v>
+        <v>0.08204040042739957</v>
       </c>
       <c r="Y7">
-        <v>-0.09521916887990625</v>
+        <v>-0.1148520667976645</v>
       </c>
       <c r="Z7">
-        <v>0.5371225367885419</v>
+        <v>3.023917152954714</v>
       </c>
       <c r="AA7">
-        <v>-0.3034748737340087</v>
+        <v>-0.7594312484589465</v>
       </c>
       <c r="AB7">
-        <v>0.09157783398265038</v>
+        <v>0.08144491196337399</v>
       </c>
       <c r="AC7">
-        <v>-0.3950527077166591</v>
+        <v>-0.8408761604223205</v>
       </c>
       <c r="AD7">
-        <v>4065.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>4065.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG7">
-        <v>1197.6</v>
+        <v>-259.1</v>
       </c>
       <c r="AH7">
-        <v>0.4790564503776319</v>
+        <v>0.01751592356687898</v>
       </c>
       <c r="AI7">
-        <v>0.4226051887576917</v>
+        <v>0.007565987447339009</v>
       </c>
       <c r="AJ7">
-        <v>0.2131378027727847</v>
+        <v>-1.104904051172708</v>
       </c>
       <c r="AK7">
-        <v>0.1773539081242781</v>
+        <v>-0.289432529043789</v>
       </c>
       <c r="AL7">
-        <v>204.5</v>
+        <v>0.146</v>
       </c>
       <c r="AM7">
-        <v>204.5</v>
+        <v>0.146</v>
       </c>
       <c r="AN7">
-        <v>-0.9022079218906025</v>
+        <v>-0.01959474504564685</v>
       </c>
       <c r="AO7">
-        <v>-22.21124694376528</v>
+        <v>-3164.383561643836</v>
       </c>
       <c r="AP7">
-        <v>-0.2657494729834684</v>
+        <v>0.5769316410598975</v>
       </c>
       <c r="AQ7">
-        <v>-22.21124694376528</v>
+        <v>-3164.383561643836</v>
       </c>
     </row>
     <row r="8">
@@ -1377,7 +1347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mercuries &amp; Associates Holding, Ltd. (TWSE:2905)</t>
+          <t>Mercuries Life Insurance Company Ltd. (TWSE:2867)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1386,109 +1356,115 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.165</v>
+        <v>-0.0949</v>
       </c>
       <c r="G8">
-        <v>0.2314895223711535</v>
+        <v>-0.7359766609203023</v>
       </c>
       <c r="H8">
-        <v>0.2314895223711535</v>
+        <v>-0.7359766609203023</v>
       </c>
       <c r="I8">
-        <v>-0.8531244100434208</v>
+        <v>-0.2509614109534544</v>
       </c>
       <c r="J8">
-        <v>-0.8531244100434208</v>
+        <v>-0.2509614109534544</v>
       </c>
       <c r="K8">
-        <v>-36</v>
+        <v>-312.5</v>
       </c>
       <c r="L8">
-        <v>-0.01359259958467057</v>
+        <v>-0.1036003182601777</v>
       </c>
       <c r="M8">
-        <v>3.54</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.008209647495361782</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>-0.09833333333333333</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>3.54</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.008209647495361782</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>-0.09833333333333333</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>660.3</v>
+        <v>434.2</v>
       </c>
       <c r="V8">
-        <v>1.531307977736549</v>
+        <v>0.5125118035882908</v>
       </c>
       <c r="W8">
-        <v>-0.05378753922008069</v>
+        <v>-0.3679500765336159</v>
       </c>
       <c r="X8">
-        <v>0.1677444127800011</v>
+        <v>0.09805454361581395</v>
       </c>
       <c r="Y8">
-        <v>-0.2215319520000818</v>
+        <v>-0.4660046201494299</v>
+      </c>
+      <c r="Z8">
+        <v>5.93195673549656</v>
+      </c>
+      <c r="AA8">
+        <v>-1.488692232055064</v>
       </c>
       <c r="AB8">
-        <v>0.09068975865201341</v>
+        <v>0.07944408749216941</v>
+      </c>
+      <c r="AC8">
+        <v>-1.568136319547234</v>
       </c>
       <c r="AD8">
-        <v>707.2</v>
+        <v>412.9</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>707.2</v>
+        <v>412.9</v>
       </c>
       <c r="AG8">
-        <v>46.90000000000009</v>
+        <v>-21.30000000000001</v>
       </c>
       <c r="AH8">
-        <v>0.6212227687983134</v>
+        <v>0.3276724069518292</v>
       </c>
       <c r="AI8">
-        <v>0.4154135338345865</v>
+        <v>0.2577885996129113</v>
       </c>
       <c r="AJ8">
-        <v>0.09809663250366049</v>
+        <v>-0.02579004722121323</v>
       </c>
       <c r="AK8">
-        <v>0.04500527780443344</v>
+        <v>-0.01824411134903641</v>
       </c>
       <c r="AL8">
-        <v>3.8</v>
+        <v>10.4</v>
       </c>
       <c r="AM8">
-        <v>3.8</v>
+        <v>10.4</v>
       </c>
       <c r="AN8">
-        <v>-0.3176142998293363</v>
+        <v>-0.5527443105756359</v>
       </c>
       <c r="AO8">
-        <v>-594.6052631578948</v>
+        <v>-72.78846153846153</v>
       </c>
       <c r="AP8">
-        <v>-0.02106350489535619</v>
+        <v>0.02851405622489961</v>
       </c>
       <c r="AQ8">
-        <v>-594.6052631578948</v>
+        <v>-72.78846153846153</v>
       </c>
     </row>
     <row r="9">
@@ -1499,7 +1475,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mercuries Life Insurance Company Ltd. (TWSE:2867)</t>
+          <t>Mercuries &amp; Associates Holding, Ltd. (TWSE:2905)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1508,106 +1484,118 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.22</v>
+        <v>-0.073</v>
       </c>
       <c r="G9">
-        <v>0.3217249106656169</v>
+        <v>-0.5413319904318268</v>
       </c>
       <c r="H9">
-        <v>0.3217249106656169</v>
+        <v>-0.5413319904318268</v>
       </c>
       <c r="I9">
-        <v>-1.409545151717037</v>
+        <v>-0.1826513911620294</v>
       </c>
       <c r="J9">
-        <v>-1.409545151717037</v>
+        <v>-0.1826513911620294</v>
       </c>
       <c r="K9">
-        <v>-205.4</v>
+        <v>-108.9</v>
       </c>
       <c r="L9">
-        <v>-0.1244019138755981</v>
+        <v>-0.02742037013722775</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>28.9</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.06066330814441646</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>-0.2653810835629017</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>28.9</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.06066330814441646</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>-0.2653810835629017</v>
       </c>
       <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
         <v>0</v>
       </c>
       <c r="U9">
         <v>614.1</v>
       </c>
       <c r="V9">
-        <v>0.8322265889686949</v>
+        <v>1.28904282115869</v>
       </c>
       <c r="W9">
-        <v>-0.137593783494105</v>
+        <v>-0.2956026058631922</v>
       </c>
       <c r="X9">
-        <v>0.1110951515452498</v>
+        <v>0.1420125350154503</v>
       </c>
       <c r="Y9">
-        <v>-0.2486889350393548</v>
+        <v>-0.4376151408786425</v>
+      </c>
+      <c r="Z9">
+        <v>9.56296653021912</v>
+      </c>
+      <c r="AA9">
+        <v>-1.746689140380448</v>
       </c>
       <c r="AB9">
-        <v>0.09288204924525259</v>
+        <v>0.07755014227946205</v>
+      </c>
+      <c r="AC9">
+        <v>-1.82423928265991</v>
       </c>
       <c r="AD9">
-        <v>273.3</v>
+        <v>846.2</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>273.3</v>
+        <v>846.2</v>
       </c>
       <c r="AG9">
-        <v>-340.8</v>
+        <v>232.1</v>
       </c>
       <c r="AH9">
-        <v>0.2702729430379747</v>
+        <v>0.6398003931649782</v>
       </c>
       <c r="AI9">
-        <v>0.243452699091395</v>
+        <v>0.3747232308918608</v>
       </c>
       <c r="AJ9">
-        <v>-0.8582221102996728</v>
+        <v>0.3275935074100212</v>
       </c>
       <c r="AK9">
-        <v>-0.6702064896755163</v>
+        <v>0.1411714615899276</v>
       </c>
       <c r="AL9">
-        <v>9.779999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AM9">
-        <v>9.779999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AN9">
-        <v>-0.1179084516156866</v>
+        <v>-1.222655685594567</v>
       </c>
       <c r="AO9">
-        <v>-237.9652351738242</v>
+        <v>-93</v>
       </c>
       <c r="AP9">
-        <v>0.1470296388972777</v>
+        <v>-0.3353561624042768</v>
       </c>
       <c r="AQ9">
-        <v>-237.9652351738242</v>
+        <v>-93</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/taiwan/taiwan_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.073</v>
+        <v>-0.0008500000000000001</v>
       </c>
       <c r="E2">
-        <v>-0.0427</v>
+        <v>0.185</v>
       </c>
       <c r="F2">
-        <v>0.204</v>
+        <v>0.313</v>
       </c>
       <c r="G2">
-        <v>-0.2808894009293091</v>
+        <v>0.1474237794279774</v>
       </c>
       <c r="H2">
-        <v>-0.2808894009293091</v>
+        <v>0.1474237794279774</v>
       </c>
       <c r="I2">
-        <v>0.02139170594123672</v>
+        <v>0.2724407467613085</v>
       </c>
       <c r="J2">
-        <v>0.02024134000881314</v>
+        <v>0.2380583275356009</v>
       </c>
       <c r="K2">
-        <v>1975.3</v>
+        <v>7700.6</v>
       </c>
       <c r="L2">
-        <v>0.03279143003703624</v>
+        <v>0.1274718507801663</v>
       </c>
       <c r="M2">
-        <v>1056.9</v>
+        <v>2213</v>
       </c>
       <c r="N2">
-        <v>0.01599187771789292</v>
+        <v>0.02842335775798404</v>
       </c>
       <c r="O2">
-        <v>0.5350579658786007</v>
+        <v>0.2873802041399371</v>
       </c>
       <c r="P2">
-        <v>1056.9</v>
+        <v>2213</v>
       </c>
       <c r="Q2">
-        <v>0.01599187771789292</v>
+        <v>0.02842335775798404</v>
       </c>
       <c r="R2">
-        <v>0.5350579658786007</v>
+        <v>0.2873802041399371</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>34403.2</v>
+        <v>35788.8</v>
       </c>
       <c r="V2">
-        <v>0.5205523393927656</v>
+        <v>0.4596646480474194</v>
       </c>
       <c r="W2">
-        <v>-0.03281166637026498</v>
+        <v>0.1458467119292139</v>
       </c>
       <c r="X2">
-        <v>0.1167021088638113</v>
+        <v>0.107648658707144</v>
       </c>
       <c r="Y2">
-        <v>-0.1495137752340763</v>
+        <v>0.0381980532220699</v>
       </c>
       <c r="Z2">
-        <v>0.9064599887592178</v>
+        <v>0.8063111221448526</v>
       </c>
       <c r="AA2">
-        <v>-0.1597911853829768</v>
+        <v>0.2572778808008162</v>
       </c>
       <c r="AB2">
-        <v>0.08125388517380022</v>
+        <v>0.08416103427221169</v>
       </c>
       <c r="AC2">
-        <v>-0.2380528735434169</v>
+        <v>0.172859231655436</v>
       </c>
       <c r="AD2">
-        <v>62248.7</v>
+        <v>56089.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>62248.7</v>
+        <v>56089.8</v>
       </c>
       <c r="AG2">
-        <v>27845.5</v>
+        <v>20301</v>
       </c>
       <c r="AH2">
-        <v>0.4850352778005041</v>
+        <v>0.4187421564887349</v>
       </c>
       <c r="AI2">
-        <v>0.4975644809075127</v>
+        <v>0.4472457093283237</v>
       </c>
       <c r="AJ2">
-        <v>0.2964327574404936</v>
+        <v>0.2068164568890428</v>
       </c>
       <c r="AK2">
-        <v>0.3069944302100467</v>
+        <v>0.2265160204769322</v>
       </c>
       <c r="AL2">
-        <v>5131.546</v>
+        <v>5952.4</v>
       </c>
       <c r="AM2">
-        <v>5131.546</v>
+        <v>5952.4</v>
       </c>
       <c r="AN2">
-        <v>36.4923789424317</v>
+        <v>3.33955321631856</v>
       </c>
       <c r="AO2">
-        <v>0.2511134071486448</v>
+        <v>2.764968752099993</v>
       </c>
       <c r="AP2">
-        <v>16.32401219369211</v>
+        <v>1.208709423896735</v>
       </c>
       <c r="AQ2">
-        <v>0.2511134071486448</v>
+        <v>2.764968752099993</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fubon Financial Holding Co., Ltd. (TWSE:2881)</t>
+          <t>Cathay Financial Holding Co., Ltd. (TWSE:2882)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,49 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0617</v>
+        <v>0.0213</v>
       </c>
       <c r="E3">
-        <v>-0.124</v>
+        <v>0.144</v>
       </c>
       <c r="F3">
-        <v>0.204</v>
+        <v>0.343</v>
       </c>
       <c r="G3">
-        <v>-0.09763021830716201</v>
+        <v>0.095643736532379</v>
       </c>
       <c r="H3">
-        <v>-0.09763021830716201</v>
+        <v>0.095643736532379</v>
       </c>
       <c r="I3">
-        <v>0.1512351589429337</v>
+        <v>0.2316493819070782</v>
       </c>
       <c r="J3">
-        <v>0.1305132350611976</v>
+        <v>0.2003479872318476</v>
       </c>
       <c r="K3">
-        <v>964.1</v>
+        <v>2975.2</v>
       </c>
       <c r="L3">
-        <v>0.04615568747606281</v>
+        <v>0.09372834154516929</v>
       </c>
       <c r="M3">
-        <v>577.8</v>
+        <v>923.7</v>
       </c>
       <c r="N3">
-        <v>0.01869249582670135</v>
+        <v>0.0302216318437911</v>
       </c>
       <c r="O3">
-        <v>0.5993154237112333</v>
+        <v>0.3104665232589406</v>
       </c>
       <c r="P3">
-        <v>577.8</v>
+        <v>923.7</v>
       </c>
       <c r="Q3">
-        <v>0.01869249582670135</v>
+        <v>0.0302216318437911</v>
       </c>
       <c r="R3">
-        <v>0.5993154237112333</v>
+        <v>0.3104665232589406</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,73 +776,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>9047.700000000001</v>
+        <v>22493.7</v>
       </c>
       <c r="V3">
-        <v>0.2927035210994216</v>
+        <v>0.7359492478128006</v>
       </c>
       <c r="W3">
-        <v>0.05717284690059242</v>
+        <v>0.1458467119292139</v>
       </c>
       <c r="X3">
-        <v>0.1018252904872283</v>
+        <v>0.107648658707144</v>
       </c>
       <c r="Y3">
-        <v>-0.04465244358663588</v>
+        <v>0.0381980532220699</v>
       </c>
       <c r="Z3">
-        <v>0.8605020968765191</v>
+        <v>1.377923053215087</v>
       </c>
       <c r="AA3">
-        <v>0.1123069124402985</v>
+        <v>0.2760641102720047</v>
       </c>
       <c r="AB3">
-        <v>0.08130099504511885</v>
+        <v>0.08416103427221169</v>
       </c>
       <c r="AC3">
-        <v>0.03100591739517969</v>
+        <v>0.191903075999793</v>
       </c>
       <c r="AD3">
-        <v>18482.5</v>
+        <v>20934.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>18482.5</v>
+        <v>20934.5</v>
       </c>
       <c r="AG3">
-        <v>9434.799999999999</v>
+        <v>-1559.200000000001</v>
       </c>
       <c r="AH3">
-        <v>0.3741904266368111</v>
+        <v>0.4065054069326022</v>
       </c>
       <c r="AI3">
-        <v>0.4421597827777179</v>
+        <v>0.4145765712599587</v>
       </c>
       <c r="AJ3">
-        <v>0.2338495399746193</v>
+        <v>-0.05375624892259958</v>
       </c>
       <c r="AK3">
-        <v>0.2880608680784543</v>
+        <v>-0.05568094163357429</v>
       </c>
       <c r="AL3">
-        <v>2908.1</v>
+        <v>2129</v>
       </c>
       <c r="AM3">
-        <v>2908.1</v>
+        <v>2129</v>
       </c>
       <c r="AN3">
-        <v>5.594654316503209</v>
+        <v>2.778411881030433</v>
       </c>
       <c r="AO3">
-        <v>1.086276262852034</v>
+        <v>3.453828088304368</v>
       </c>
       <c r="AP3">
-        <v>2.855914759656133</v>
+        <v>-0.2069359098570614</v>
       </c>
       <c r="AQ3">
-        <v>1.086276262852034</v>
+        <v>3.453828088304368</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cathay Financial Holding Co., Ltd. (TWSE:2882)</t>
+          <t>Fubon Financial Holding Co., Ltd. (TWSE:2881)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -861,44 +861,50 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.0008500000000000001</v>
+      </c>
+      <c r="E4">
+        <v>0.185</v>
+      </c>
       <c r="F4">
-        <v>0.212</v>
+        <v>0.283</v>
       </c>
       <c r="G4">
-        <v>-0.2608286457493671</v>
+        <v>0.2223143813722371</v>
       </c>
       <c r="H4">
-        <v>-0.2608286457493671</v>
+        <v>0.2223143813722371</v>
       </c>
       <c r="I4">
-        <v>0.0496368302491863</v>
+        <v>0.3448393400899877</v>
       </c>
       <c r="J4">
-        <v>0.04281818148526557</v>
+        <v>0.3104472396904273</v>
       </c>
       <c r="K4">
-        <v>1327.5</v>
+        <v>3762.9</v>
       </c>
       <c r="L4">
-        <v>0.05784137303001651</v>
+        <v>0.1425146570922147</v>
       </c>
       <c r="M4">
-        <v>410.3</v>
+        <v>1024.4</v>
       </c>
       <c r="N4">
-        <v>0.01873122540470952</v>
+        <v>0.02721218544875933</v>
       </c>
       <c r="O4">
-        <v>0.3090772128060263</v>
+        <v>0.27223683860852</v>
       </c>
       <c r="P4">
-        <v>410.3</v>
+        <v>1024.4</v>
       </c>
       <c r="Q4">
-        <v>0.01873122540470952</v>
+        <v>0.02721218544875933</v>
       </c>
       <c r="R4">
-        <v>0.3090772128060263</v>
+        <v>0.27223683860852</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -907,73 +913,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>19735.6</v>
+        <v>10244.2</v>
       </c>
       <c r="V4">
-        <v>0.9009797028934562</v>
+        <v>0.2721271672922495</v>
       </c>
       <c r="W4">
-        <v>0.1509586299438241</v>
+        <v>0.1678464853002181</v>
       </c>
       <c r="X4">
-        <v>0.1167021088638113</v>
+        <v>0.1022816634424595</v>
       </c>
       <c r="Y4">
-        <v>0.03425652108001272</v>
+        <v>0.06556482185775862</v>
       </c>
       <c r="Z4">
-        <v>1.359405078511393</v>
+        <v>0.8287330274135127</v>
       </c>
       <c r="AA4">
-        <v>0.05820725336369253</v>
+        <v>0.2572778808008162</v>
       </c>
       <c r="AB4">
-        <v>0.08125388517380022</v>
+        <v>0.08441864914538018</v>
       </c>
       <c r="AC4">
-        <v>-0.02304663181010769</v>
+        <v>0.172859231655436</v>
       </c>
       <c r="AD4">
-        <v>22652.1</v>
+        <v>19463.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>22652.1</v>
+        <v>19463.5</v>
       </c>
       <c r="AG4">
-        <v>2916.5</v>
+        <v>9219.299999999999</v>
       </c>
       <c r="AH4">
-        <v>0.5083881885328132</v>
+        <v>0.3408167625077922</v>
       </c>
       <c r="AI4">
-        <v>0.5153744821137268</v>
+        <v>0.3925232325513859</v>
       </c>
       <c r="AJ4">
-        <v>0.1175008359822893</v>
+        <v>0.1967237251462737</v>
       </c>
       <c r="AK4">
-        <v>0.1204314306832775</v>
+        <v>0.2343409233021702</v>
       </c>
       <c r="AL4">
-        <v>1695.4</v>
+        <v>3823.4</v>
       </c>
       <c r="AM4">
-        <v>1695.4</v>
+        <v>3823.4</v>
       </c>
       <c r="AN4">
-        <v>17.16848567530695</v>
+        <v>2.101685581314991</v>
       </c>
       <c r="AO4">
-        <v>0.6719358263536629</v>
+        <v>2.381388293142229</v>
       </c>
       <c r="AP4">
-        <v>2.210474458087009</v>
+        <v>0.9955079959831118</v>
       </c>
       <c r="AQ4">
-        <v>0.6719358263536629</v>
+        <v>2.381388293142229</v>
       </c>
     </row>
     <row r="5">
@@ -984,7 +990,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>China Development Financial Holding Corporation (TWSE:2883)</t>
+          <t>KGI Financial Holding Co., Ltd. (TWSE:2883)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -992,610 +998,110 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>-0.221</v>
+      </c>
       <c r="E5">
-        <v>0.0386</v>
+        <v>0.251</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>421.3</v>
+        <v>962.5</v>
+      </c>
+      <c r="L5">
+        <v>0.4251700680272109</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>264.9</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.02745248409227517</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.2752207792207792</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>264.9</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.02745248409227517</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.2752207792207792</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>2040.2</v>
+        <v>3050.9</v>
       </c>
       <c r="V5">
-        <v>0.2957797526711803</v>
+        <v>0.3161750989698842</v>
       </c>
       <c r="W5">
-        <v>0.08794672678690715</v>
+        <v>0.1411600791963042</v>
       </c>
       <c r="X5">
-        <v>0.1548897717622041</v>
+        <v>0.1377352511404091</v>
       </c>
       <c r="Y5">
-        <v>-0.06694304497529699</v>
+        <v>0.003424828055895029</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>0.1130498182254005</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.08192197659248544</v>
+        <v>0.08402034337088954</v>
       </c>
       <c r="AC5">
-        <v>-0.08192197659248544</v>
+        <v>-0.08402034337088954</v>
       </c>
       <c r="AD5">
-        <v>14856.3</v>
+        <v>15691.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>14856.3</v>
+        <v>15691.8</v>
       </c>
       <c r="AG5">
-        <v>12816.1</v>
+        <v>12640.9</v>
       </c>
       <c r="AH5">
-        <v>0.6829226808862737</v>
+        <v>0.6192208735182233</v>
       </c>
       <c r="AI5">
-        <v>0.670099186749841</v>
+        <v>0.6194971160565181</v>
       </c>
       <c r="AJ5">
-        <v>0.6501080461402672</v>
+        <v>0.5671031794098779</v>
       </c>
       <c r="AK5">
-        <v>0.6366635039070844</v>
+        <v>0.5673908164639346</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Shin Kong Financial Holding Co., Ltd. (TWSE:2888)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>-0.09130000000000001</v>
-      </c>
-      <c r="F6">
-        <v>0.15</v>
-      </c>
-      <c r="G6">
-        <v>-0.5087360177493694</v>
-      </c>
-      <c r="H6">
-        <v>-0.5087360177493694</v>
-      </c>
-      <c r="I6">
-        <v>-0.1406743175605182</v>
-      </c>
-      <c r="J6">
-        <v>-0.1406743175605182</v>
-      </c>
-      <c r="K6">
-        <v>-279.3</v>
-      </c>
-      <c r="L6">
-        <v>-0.03688540827511522</v>
-      </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>2263.5</v>
-      </c>
-      <c r="V6">
-        <v>0.496436012720693</v>
-      </c>
-      <c r="W6">
-        <v>-0.05125993356213409</v>
-      </c>
-      <c r="X6">
-        <v>0.1187577066987725</v>
-      </c>
-      <c r="Y6">
-        <v>-0.1700176402609066</v>
-      </c>
-      <c r="Z6">
-        <v>1.135894512615883</v>
-      </c>
-      <c r="AA6">
-        <v>-0.1597911853829768</v>
-      </c>
-      <c r="AB6">
-        <v>0.07826168816044012</v>
-      </c>
-      <c r="AC6">
-        <v>-0.2380528735434169</v>
-      </c>
-      <c r="AD6">
-        <v>4989.9</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>4989.9</v>
-      </c>
-      <c r="AG6">
-        <v>2726.4</v>
-      </c>
-      <c r="AH6">
-        <v>0.5225354472532305</v>
-      </c>
-      <c r="AI6">
-        <v>0.410343494815095</v>
-      </c>
-      <c r="AJ6">
-        <v>0.3742022262177631</v>
-      </c>
-      <c r="AK6">
-        <v>0.2754829843989977</v>
-      </c>
-      <c r="AL6">
-        <v>509.7</v>
-      </c>
-      <c r="AM6">
-        <v>509.7</v>
-      </c>
-      <c r="AN6">
-        <v>-4.849271137026239</v>
-      </c>
-      <c r="AO6">
-        <v>-2.089856778497155</v>
-      </c>
-      <c r="AP6">
-        <v>-2.649562682215743</v>
-      </c>
-      <c r="AQ6">
-        <v>-2.089856778497155</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Farglory Life Insurance Co., Ltd. (TPEX:5859)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>-0.0358</v>
-      </c>
-      <c r="G7">
-        <v>-0.3656773211567733</v>
-      </c>
-      <c r="H7">
-        <v>-0.3656773211567733</v>
-      </c>
-      <c r="I7">
-        <v>-0.2511415525114155</v>
-      </c>
-      <c r="J7">
-        <v>-0.2511415525114155</v>
-      </c>
-      <c r="K7">
-        <v>-36.9</v>
-      </c>
-      <c r="L7">
-        <v>-0.0200587084148728</v>
-      </c>
-      <c r="M7">
-        <v>39.9</v>
-      </c>
-      <c r="N7">
-        <v>0.08083468395461912</v>
-      </c>
-      <c r="O7">
-        <v>-1.08130081300813</v>
-      </c>
-      <c r="P7">
-        <v>39.9</v>
-      </c>
-      <c r="Q7">
-        <v>0.08083468395461912</v>
-      </c>
-      <c r="R7">
-        <v>-1.08130081300813</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>267.9</v>
-      </c>
-      <c r="V7">
-        <v>0.5427471636952997</v>
-      </c>
-      <c r="W7">
-        <v>-0.03281166637026498</v>
-      </c>
-      <c r="X7">
-        <v>0.08204040042739957</v>
-      </c>
-      <c r="Y7">
-        <v>-0.1148520667976645</v>
-      </c>
-      <c r="Z7">
-        <v>3.023917152954714</v>
-      </c>
-      <c r="AA7">
-        <v>-0.7594312484589465</v>
-      </c>
-      <c r="AB7">
-        <v>0.08144491196337399</v>
-      </c>
-      <c r="AC7">
-        <v>-0.8408761604223205</v>
-      </c>
-      <c r="AD7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG7">
-        <v>-259.1</v>
-      </c>
-      <c r="AH7">
-        <v>0.01751592356687898</v>
-      </c>
-      <c r="AI7">
-        <v>0.007565987447339009</v>
-      </c>
-      <c r="AJ7">
-        <v>-1.104904051172708</v>
-      </c>
-      <c r="AK7">
-        <v>-0.289432529043789</v>
-      </c>
-      <c r="AL7">
-        <v>0.146</v>
-      </c>
-      <c r="AM7">
-        <v>0.146</v>
-      </c>
-      <c r="AN7">
-        <v>-0.01959474504564685</v>
-      </c>
-      <c r="AO7">
-        <v>-3164.383561643836</v>
-      </c>
-      <c r="AP7">
-        <v>0.5769316410598975</v>
-      </c>
-      <c r="AQ7">
-        <v>-3164.383561643836</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Mercuries Life Insurance Company Ltd. (TWSE:2867)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>-0.0949</v>
-      </c>
-      <c r="G8">
-        <v>-0.7359766609203023</v>
-      </c>
-      <c r="H8">
-        <v>-0.7359766609203023</v>
-      </c>
-      <c r="I8">
-        <v>-0.2509614109534544</v>
-      </c>
-      <c r="J8">
-        <v>-0.2509614109534544</v>
-      </c>
-      <c r="K8">
-        <v>-312.5</v>
-      </c>
-      <c r="L8">
-        <v>-0.1036003182601777</v>
-      </c>
-      <c r="M8">
-        <v>-0</v>
-      </c>
-      <c r="N8">
-        <v>-0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>-0</v>
-      </c>
-      <c r="Q8">
-        <v>-0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>434.2</v>
-      </c>
-      <c r="V8">
-        <v>0.5125118035882908</v>
-      </c>
-      <c r="W8">
-        <v>-0.3679500765336159</v>
-      </c>
-      <c r="X8">
-        <v>0.09805454361581395</v>
-      </c>
-      <c r="Y8">
-        <v>-0.4660046201494299</v>
-      </c>
-      <c r="Z8">
-        <v>5.93195673549656</v>
-      </c>
-      <c r="AA8">
-        <v>-1.488692232055064</v>
-      </c>
-      <c r="AB8">
-        <v>0.07944408749216941</v>
-      </c>
-      <c r="AC8">
-        <v>-1.568136319547234</v>
-      </c>
-      <c r="AD8">
-        <v>412.9</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>412.9</v>
-      </c>
-      <c r="AG8">
-        <v>-21.30000000000001</v>
-      </c>
-      <c r="AH8">
-        <v>0.3276724069518292</v>
-      </c>
-      <c r="AI8">
-        <v>0.2577885996129113</v>
-      </c>
-      <c r="AJ8">
-        <v>-0.02579004722121323</v>
-      </c>
-      <c r="AK8">
-        <v>-0.01824411134903641</v>
-      </c>
-      <c r="AL8">
-        <v>10.4</v>
-      </c>
-      <c r="AM8">
-        <v>10.4</v>
-      </c>
-      <c r="AN8">
-        <v>-0.5527443105756359</v>
-      </c>
-      <c r="AO8">
-        <v>-72.78846153846153</v>
-      </c>
-      <c r="AP8">
-        <v>0.02851405622489961</v>
-      </c>
-      <c r="AQ8">
-        <v>-72.78846153846153</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Mercuries &amp; Associates Holding, Ltd. (TWSE:2905)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>-0.073</v>
-      </c>
-      <c r="G9">
-        <v>-0.5413319904318268</v>
-      </c>
-      <c r="H9">
-        <v>-0.5413319904318268</v>
-      </c>
-      <c r="I9">
-        <v>-0.1826513911620294</v>
-      </c>
-      <c r="J9">
-        <v>-0.1826513911620294</v>
-      </c>
-      <c r="K9">
-        <v>-108.9</v>
-      </c>
-      <c r="L9">
-        <v>-0.02742037013722775</v>
-      </c>
-      <c r="M9">
-        <v>28.9</v>
-      </c>
-      <c r="N9">
-        <v>0.06066330814441646</v>
-      </c>
-      <c r="O9">
-        <v>-0.2653810835629017</v>
-      </c>
-      <c r="P9">
-        <v>28.9</v>
-      </c>
-      <c r="Q9">
-        <v>0.06066330814441646</v>
-      </c>
-      <c r="R9">
-        <v>-0.2653810835629017</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>614.1</v>
-      </c>
-      <c r="V9">
-        <v>1.28904282115869</v>
-      </c>
-      <c r="W9">
-        <v>-0.2956026058631922</v>
-      </c>
-      <c r="X9">
-        <v>0.1420125350154503</v>
-      </c>
-      <c r="Y9">
-        <v>-0.4376151408786425</v>
-      </c>
-      <c r="Z9">
-        <v>9.56296653021912</v>
-      </c>
-      <c r="AA9">
-        <v>-1.746689140380448</v>
-      </c>
-      <c r="AB9">
-        <v>0.07755014227946205</v>
-      </c>
-      <c r="AC9">
-        <v>-1.82423928265991</v>
-      </c>
-      <c r="AD9">
-        <v>846.2</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>846.2</v>
-      </c>
-      <c r="AG9">
-        <v>232.1</v>
-      </c>
-      <c r="AH9">
-        <v>0.6398003931649782</v>
-      </c>
-      <c r="AI9">
-        <v>0.3747232308918608</v>
-      </c>
-      <c r="AJ9">
-        <v>0.3275935074100212</v>
-      </c>
-      <c r="AK9">
-        <v>0.1411714615899276</v>
-      </c>
-      <c r="AL9">
-        <v>7.8</v>
-      </c>
-      <c r="AM9">
-        <v>7.8</v>
-      </c>
-      <c r="AN9">
-        <v>-1.222655685594567</v>
-      </c>
-      <c r="AO9">
-        <v>-93</v>
-      </c>
-      <c r="AP9">
-        <v>-0.3353561624042768</v>
-      </c>
-      <c r="AQ9">
-        <v>-93</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/taiwan/taiwan_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0008500000000000001</v>
+        <v>-0.0411</v>
       </c>
       <c r="E2">
         <v>0.185</v>
@@ -597,40 +597,40 @@
         <v>0.313</v>
       </c>
       <c r="G2">
-        <v>0.1474237794279774</v>
+        <v>0.090212194157838</v>
       </c>
       <c r="H2">
-        <v>0.1474237794279774</v>
+        <v>0.090212194157838</v>
       </c>
       <c r="I2">
-        <v>0.2724407467613085</v>
+        <v>0.21646520928764</v>
       </c>
       <c r="J2">
-        <v>0.2380583275356009</v>
+        <v>0.204757398645221</v>
       </c>
       <c r="K2">
-        <v>7700.6</v>
+        <v>8136</v>
       </c>
       <c r="L2">
-        <v>0.1274718507801663</v>
+        <v>0.09956812204682493</v>
       </c>
       <c r="M2">
-        <v>2213</v>
+        <v>2230.3</v>
       </c>
       <c r="N2">
-        <v>0.02842335775798404</v>
+        <v>0.02576567480236458</v>
       </c>
       <c r="O2">
-        <v>0.2873802041399371</v>
+        <v>0.2741273352999017</v>
       </c>
       <c r="P2">
-        <v>2213</v>
+        <v>2230.3</v>
       </c>
       <c r="Q2">
-        <v>0.02842335775798404</v>
+        <v>0.02576567480236458</v>
       </c>
       <c r="R2">
-        <v>0.2873802041399371</v>
+        <v>0.2741273352999017</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>35788.8</v>
+        <v>41831.4</v>
       </c>
       <c r="V2">
-        <v>0.4596646480474194</v>
+        <v>0.4832597627797308</v>
       </c>
       <c r="W2">
-        <v>0.1458467119292139</v>
+        <v>0.1411600791963042</v>
       </c>
       <c r="X2">
-        <v>0.107648658707144</v>
+        <v>0.1120333657442411</v>
       </c>
       <c r="Y2">
-        <v>0.0381980532220699</v>
+        <v>0.02912671345206305</v>
       </c>
       <c r="Z2">
-        <v>0.8063111221448526</v>
+        <v>0.9332185933579487</v>
       </c>
       <c r="AA2">
-        <v>0.2572778808008162</v>
+        <v>0.08642782426778241</v>
       </c>
       <c r="AB2">
-        <v>0.08416103427221169</v>
+        <v>0.08400399474525871</v>
       </c>
       <c r="AC2">
-        <v>0.172859231655436</v>
+        <v>0.006294697221419537</v>
       </c>
       <c r="AD2">
-        <v>56089.8</v>
+        <v>64149.62</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>56089.8</v>
+        <v>64149.62</v>
       </c>
       <c r="AG2">
-        <v>20301</v>
+        <v>22318.22</v>
       </c>
       <c r="AH2">
-        <v>0.4187421564887349</v>
+        <v>0.425647924245766</v>
       </c>
       <c r="AI2">
-        <v>0.4472457093283237</v>
+        <v>0.4364174453175566</v>
       </c>
       <c r="AJ2">
-        <v>0.2068164568890428</v>
+        <v>0.2049816346788989</v>
       </c>
       <c r="AK2">
-        <v>0.2265160204769322</v>
+        <v>0.2122310360914728</v>
       </c>
       <c r="AL2">
-        <v>5952.4</v>
+        <v>6616.703</v>
       </c>
       <c r="AM2">
-        <v>5952.4</v>
+        <v>6616.703</v>
       </c>
       <c r="AN2">
-        <v>3.33955321631856</v>
+        <v>3.540422314450969</v>
       </c>
       <c r="AO2">
-        <v>2.764968752099993</v>
+        <v>2.673234691053837</v>
       </c>
       <c r="AP2">
-        <v>1.208709423896735</v>
+        <v>1.231744227118195</v>
       </c>
       <c r="AQ2">
-        <v>2.764968752099993</v>
+        <v>2.673234691053837</v>
       </c>
     </row>
     <row r="3">
@@ -785,10 +785,10 @@
         <v>0.1458467119292139</v>
       </c>
       <c r="X3">
-        <v>0.107648658707144</v>
+        <v>0.1076197747737654</v>
       </c>
       <c r="Y3">
-        <v>0.0381980532220699</v>
+        <v>0.03822693715544857</v>
       </c>
       <c r="Z3">
         <v>1.377923053215087</v>
@@ -797,10 +797,10 @@
         <v>0.2760641102720047</v>
       </c>
       <c r="AB3">
-        <v>0.08416103427221169</v>
+        <v>0.08414389181392493</v>
       </c>
       <c r="AC3">
-        <v>0.191903075999793</v>
+        <v>0.1919202184580798</v>
       </c>
       <c r="AD3">
         <v>20934.5</v>
@@ -922,10 +922,10 @@
         <v>0.1678464853002181</v>
       </c>
       <c r="X4">
-        <v>0.1022816634424595</v>
+        <v>0.1022552859487823</v>
       </c>
       <c r="Y4">
-        <v>0.06556482185775862</v>
+        <v>0.0655911993514358</v>
       </c>
       <c r="Z4">
         <v>0.8287330274135127</v>
@@ -934,10 +934,10 @@
         <v>0.2572778808008162</v>
       </c>
       <c r="AB4">
-        <v>0.08441864914538018</v>
+        <v>0.08440126154370112</v>
       </c>
       <c r="AC4">
-        <v>0.172859231655436</v>
+        <v>0.1728766192571151</v>
       </c>
       <c r="AD4">
         <v>19463.5</v>
@@ -990,118 +990,639 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Shin Kong Financial Holding Co., Ltd. (TWSE:2888)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>-0.0411</v>
+      </c>
+      <c r="E5">
+        <v>0.0327</v>
+      </c>
+      <c r="G5">
+        <v>-0.05221290808779064</v>
+      </c>
+      <c r="H5">
+        <v>-0.05221290808779064</v>
+      </c>
+      <c r="I5">
+        <v>0.1292204348594662</v>
+      </c>
+      <c r="J5">
+        <v>0.1292204348594662</v>
+      </c>
+      <c r="K5">
+        <v>409.9</v>
+      </c>
+      <c r="L5">
+        <v>0.03813626340909725</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>3430.2</v>
+      </c>
+      <c r="V5">
+        <v>0.5343323571562091</v>
+      </c>
+      <c r="W5">
+        <v>0.05801840056617126</v>
+      </c>
+      <c r="X5">
+        <v>0.1143688033877972</v>
+      </c>
+      <c r="Y5">
+        <v>-0.05635040282162591</v>
+      </c>
+      <c r="Z5">
+        <v>1.09552445699259</v>
+      </c>
+      <c r="AA5">
+        <v>0.141564146731763</v>
+      </c>
+      <c r="AB5">
+        <v>0.08214558755948004</v>
+      </c>
+      <c r="AC5">
+        <v>0.05941855917228298</v>
+      </c>
+      <c r="AD5">
+        <v>5753.1</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>5753.1</v>
+      </c>
+      <c r="AG5">
+        <v>2322.900000000001</v>
+      </c>
+      <c r="AH5">
+        <v>0.472623164951079</v>
+      </c>
+      <c r="AI5">
+        <v>0.3885575734653492</v>
+      </c>
+      <c r="AJ5">
+        <v>0.2657020303116958</v>
+      </c>
+      <c r="AK5">
+        <v>0.2041912430446287</v>
+      </c>
+      <c r="AL5">
+        <v>643.9</v>
+      </c>
+      <c r="AM5">
+        <v>643.9</v>
+      </c>
+      <c r="AN5">
+        <v>4.036413386655441</v>
+      </c>
+      <c r="AO5">
+        <v>2.15701195837863</v>
+      </c>
+      <c r="AP5">
+        <v>1.629762155335719</v>
+      </c>
+      <c r="AQ5">
+        <v>2.15701195837863</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mercuries &amp; Associates Holding, Ltd. (TWSE:2905)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>-0.0365</v>
+      </c>
+      <c r="G6">
+        <v>-0.09821465815709339</v>
+      </c>
+      <c r="H6">
+        <v>-0.09821465815709339</v>
+      </c>
+      <c r="I6">
+        <v>0.01378634296917365</v>
+      </c>
+      <c r="J6">
+        <v>0.01378634296917365</v>
+      </c>
+      <c r="K6">
+        <v>-34.8</v>
+      </c>
+      <c r="L6">
+        <v>-0.007258165436115629</v>
+      </c>
+      <c r="M6">
+        <v>17.3</v>
+      </c>
+      <c r="N6">
+        <v>0.03478785441383471</v>
+      </c>
+      <c r="O6">
+        <v>-0.4971264367816093</v>
+      </c>
+      <c r="P6">
+        <v>17.3</v>
+      </c>
+      <c r="Q6">
+        <v>0.03478785441383471</v>
+      </c>
+      <c r="R6">
+        <v>-0.4971264367816093</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1549.7</v>
+      </c>
+      <c r="V6">
+        <v>3.116227629197668</v>
+      </c>
+      <c r="W6">
+        <v>-0.06532757649709028</v>
+      </c>
+      <c r="X6">
+        <v>0.1754939355826437</v>
+      </c>
+      <c r="Y6">
+        <v>-0.240821512079734</v>
+      </c>
+      <c r="Z6">
+        <v>6.269089958158996</v>
+      </c>
+      <c r="AA6">
+        <v>0.08642782426778241</v>
+      </c>
+      <c r="AB6">
+        <v>0.08013312704636287</v>
+      </c>
+      <c r="AC6">
+        <v>0.006294697221419537</v>
+      </c>
+      <c r="AD6">
+        <v>1397.1</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>1397.1</v>
+      </c>
+      <c r="AG6">
+        <v>-152.6000000000001</v>
+      </c>
+      <c r="AH6">
+        <v>0.7374894425675675</v>
+      </c>
+      <c r="AI6">
+        <v>0.4570914444626206</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.4427038004061508</v>
+      </c>
+      <c r="AK6">
+        <v>-0.1012742235200426</v>
+      </c>
+      <c r="AL6">
+        <v>7.53</v>
+      </c>
+      <c r="AM6">
+        <v>7.53</v>
+      </c>
+      <c r="AN6">
+        <v>13.6435546875</v>
+      </c>
+      <c r="AO6">
+        <v>8.778220451527224</v>
+      </c>
+      <c r="AP6">
+        <v>-1.490234375000001</v>
+      </c>
+      <c r="AQ6">
+        <v>8.778220451527224</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mercuries Life Insurance Company Ltd. (TWSE:2867)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>-0.0516</v>
+      </c>
+      <c r="G7">
+        <v>-0.1414257161892072</v>
+      </c>
+      <c r="H7">
+        <v>-0.1414257161892072</v>
+      </c>
+      <c r="I7">
+        <v>0.004343770819453698</v>
+      </c>
+      <c r="J7">
+        <v>0.004343770819453698</v>
+      </c>
+      <c r="K7">
+        <v>-150.2</v>
+      </c>
+      <c r="L7">
+        <v>-0.04002664890073284</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>815.1</v>
+      </c>
+      <c r="V7">
+        <v>0.7429587093245831</v>
+      </c>
+      <c r="W7">
+        <v>-0.1263458950201884</v>
+      </c>
+      <c r="X7">
+        <v>0.1120333657442411</v>
+      </c>
+      <c r="Y7">
+        <v>-0.2383792607644295</v>
+      </c>
+      <c r="Z7">
+        <v>3.214132762312635</v>
+      </c>
+      <c r="AA7">
+        <v>0.01396145610278373</v>
+      </c>
+      <c r="AB7">
+        <v>0.08230625340484053</v>
+      </c>
+      <c r="AC7">
+        <v>-0.06834479730205681</v>
+      </c>
+      <c r="AD7">
+        <v>903</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>903</v>
+      </c>
+      <c r="AG7">
+        <v>87.89999999999998</v>
+      </c>
+      <c r="AH7">
+        <v>0.4514774261286936</v>
+      </c>
+      <c r="AI7">
+        <v>0.394616090547568</v>
+      </c>
+      <c r="AJ7">
+        <v>0.0741772151898734</v>
+      </c>
+      <c r="AK7">
+        <v>0.05966603312516969</v>
+      </c>
+      <c r="AL7">
+        <v>12.7</v>
+      </c>
+      <c r="AM7">
+        <v>12.7</v>
+      </c>
+      <c r="AN7">
+        <v>34.0754716981132</v>
+      </c>
+      <c r="AO7">
+        <v>1.283464566929134</v>
+      </c>
+      <c r="AP7">
+        <v>3.316981132075471</v>
+      </c>
+      <c r="AQ7">
+        <v>1.283464566929134</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>KGI Financial Holding Co., Ltd. (TWSE:2883)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D5">
+      <c r="D8">
         <v>-0.221</v>
       </c>
-      <c r="E5">
+      <c r="E8">
         <v>0.251</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>962.5</v>
       </c>
-      <c r="L5">
+      <c r="L8">
         <v>0.4251700680272109</v>
       </c>
-      <c r="M5">
+      <c r="M8">
         <v>264.9</v>
       </c>
-      <c r="N5">
+      <c r="N8">
         <v>0.02745248409227517</v>
       </c>
-      <c r="O5">
+      <c r="O8">
         <v>0.2752207792207792</v>
       </c>
-      <c r="P5">
+      <c r="P8">
         <v>264.9</v>
       </c>
-      <c r="Q5">
+      <c r="Q8">
         <v>0.02745248409227517</v>
       </c>
-      <c r="R5">
+      <c r="R8">
         <v>0.2752207792207792</v>
       </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
         <v>3050.9</v>
       </c>
-      <c r="V5">
+      <c r="V8">
         <v>0.3161750989698842</v>
       </c>
-      <c r="W5">
+      <c r="W8">
         <v>0.1411600791963042</v>
       </c>
-      <c r="X5">
-        <v>0.1377352511404091</v>
-      </c>
-      <c r="Y5">
-        <v>0.003424828055895029</v>
-      </c>
-      <c r="Z5">
+      <c r="X8">
+        <v>0.1376923164717421</v>
+      </c>
+      <c r="Y8">
+        <v>0.003467762724562062</v>
+      </c>
+      <c r="Z8">
         <v>0.1130498182254005</v>
       </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.08402034337088954</v>
-      </c>
-      <c r="AC5">
-        <v>-0.08402034337088954</v>
-      </c>
-      <c r="AD5">
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.08400399474525871</v>
+      </c>
+      <c r="AC8">
+        <v>-0.08400399474525871</v>
+      </c>
+      <c r="AD8">
         <v>15691.8</v>
       </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
         <v>15691.8</v>
       </c>
-      <c r="AG5">
+      <c r="AG8">
         <v>12640.9</v>
       </c>
-      <c r="AH5">
+      <c r="AH8">
         <v>0.6192208735182233</v>
       </c>
-      <c r="AI5">
+      <c r="AI8">
         <v>0.6194971160565181</v>
       </c>
-      <c r="AJ5">
+      <c r="AJ8">
         <v>0.5671031794098779</v>
       </c>
-      <c r="AK5">
+      <c r="AK8">
         <v>0.5673908164639346</v>
       </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Farglory Life Insurance Co., Ltd. (TPEX:5859)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>-0.0541</v>
+      </c>
+      <c r="E9">
+        <v>0.696</v>
+      </c>
+      <c r="G9">
+        <v>0.014148358491506</v>
+      </c>
+      <c r="H9">
+        <v>0.014148358491506</v>
+      </c>
+      <c r="I9">
+        <v>-0.1203108653415035</v>
+      </c>
+      <c r="J9">
+        <v>-0.1203108653415035</v>
+      </c>
+      <c r="K9">
+        <v>210.5</v>
+      </c>
+      <c r="L9">
+        <v>0.1048672345937329</v>
+      </c>
+      <c r="M9">
+        <v>-0</v>
+      </c>
+      <c r="N9">
+        <v>-0</v>
+      </c>
+      <c r="O9">
+        <v>-0</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>-0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>247.6</v>
+      </c>
+      <c r="V9">
+        <v>0.3596746077861708</v>
+      </c>
+      <c r="W9">
+        <v>0.1823616044355887</v>
+      </c>
+      <c r="X9">
+        <v>0.08604383026852008</v>
+      </c>
+      <c r="Y9">
+        <v>0.0963177741670686</v>
+      </c>
+      <c r="Z9">
+        <v>2.242292225201072</v>
+      </c>
+      <c r="AA9">
+        <v>-0.2697721179624665</v>
+      </c>
+      <c r="AB9">
+        <v>0.08566421956014791</v>
+      </c>
+      <c r="AC9">
+        <v>-0.3554363375226144</v>
+      </c>
+      <c r="AD9">
+        <v>6.62</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>6.62</v>
+      </c>
+      <c r="AG9">
+        <v>-240.98</v>
+      </c>
+      <c r="AH9">
+        <v>0.009524905758107681</v>
+      </c>
+      <c r="AI9">
+        <v>0.004633518114116133</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.5385990791649904</v>
+      </c>
+      <c r="AK9">
+        <v>-0.2040266865348144</v>
+      </c>
+      <c r="AL9">
+        <v>0.173</v>
+      </c>
+      <c r="AM9">
+        <v>0.173</v>
+      </c>
+      <c r="AN9">
+        <v>-0.02870771899392888</v>
+      </c>
+      <c r="AO9">
+        <v>-1395.953757225434</v>
+      </c>
+      <c r="AP9">
+        <v>1.04501300954033</v>
+      </c>
+      <c r="AQ9">
+        <v>-1395.953757225434</v>
       </c>
     </row>
   </sheetData>
